--- a/Architecture/Traceability to Requirements & Security Architecture – STRIDE Table.xlsx
+++ b/Architecture/Traceability to Requirements & Security Architecture – STRIDE Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harsh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harsh\Downloads\online-exam-portal-se-miniproject\Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{547745EF-EE80-4E85-8E6E-A67913C0929C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE29F02-8B83-4CF3-ACED-C4F377B10C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1D5CF0FA-2972-4598-B1E6-30762399D520}"/>
   </bookViews>
@@ -34,16 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="131">
-  <si>
-    <t>Req. ID</t>
-  </si>
-  <si>
-    <t>Requirement Description</t>
-  </si>
-  <si>
-    <t>Component(s) Responsible</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="159">
   <si>
     <t>FR-OE-001</t>
   </si>
@@ -258,9 +249,6 @@
     <t>Auto-save ≤ 1 s</t>
   </si>
   <si>
-    <t>Exam Management Service + Data Access Layer</t>
-  </si>
-  <si>
     <t>NFR-OE-003</t>
   </si>
   <si>
@@ -330,9 +318,6 @@
     <t>SEC-OE-009</t>
   </si>
   <si>
-    <t>Submission only by owner before end + 5 s</t>
-  </si>
-  <si>
     <t>SEC-OE-010</t>
   </si>
   <si>
@@ -427,13 +412,112 @@
   </si>
   <si>
     <t>Security Architecture – STRIDE Table</t>
+  </si>
+  <si>
+    <t>Req ID</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Architecture Component(s)</t>
+  </si>
+  <si>
+    <t>Exam Management Service + Data Access</t>
+  </si>
+  <si>
+    <t>NFR-OE-004</t>
+  </si>
+  <si>
+    <t>99.5 % availability in exam windows</t>
+  </si>
+  <si>
+    <t>Deployment + Monitoring</t>
+  </si>
+  <si>
+    <t>NFR-OE-005</t>
+  </si>
+  <si>
+    <t>RPO ≤ 30 s (auto-save)</t>
+  </si>
+  <si>
+    <t>NFR-OE-006</t>
+  </si>
+  <si>
+    <t>Automated backup every 24 h, retain last 7</t>
+  </si>
+  <si>
+    <t>Deployment + Audit &amp; Logging Service / Jobs</t>
+  </si>
+  <si>
+    <t>NFR-OE-007</t>
+  </si>
+  <si>
+    <t>First-time Student starts exam within 3 clicks</t>
+  </si>
+  <si>
+    <t>Presentation Layer (React)</t>
+  </si>
+  <si>
+    <t>NFR-OE-008</t>
+  </si>
+  <si>
+    <t>WCAG 2.1 Level AA (contrast + keyboard) on exam pages</t>
+  </si>
+  <si>
+    <t>NFR-OE-009</t>
+  </si>
+  <si>
+    <t>Works on latest Chrome / Firefox / Edge, ≥ 360 px</t>
+  </si>
+  <si>
+    <t>NFR-OE-011</t>
+  </si>
+  <si>
+    <t>Store ≥ 10,000 questions, 1,000 users, 200 exams</t>
+  </si>
+  <si>
+    <t>MongoDB + Data Access Layer</t>
+  </si>
+  <si>
+    <t>NFR-OE-012</t>
+  </si>
+  <si>
+    <t>Modular code + ≥ 70% unit test coverage</t>
+  </si>
+  <si>
+    <t>All Business Services (services/ folder)</t>
+  </si>
+  <si>
+    <t>NFR-OE-013</t>
+  </si>
+  <si>
+    <t>Deployable on Linux/container in ≤ 60 min</t>
+  </si>
+  <si>
+    <t>Deployment (Docker Compose – future)</t>
+  </si>
+  <si>
+    <t>NFR-OE-014</t>
+  </si>
+  <si>
+    <t>Retain attempts/results ≥ 1 year; Admin can delete</t>
+  </si>
+  <si>
+    <t>MongoDB + Authentication &amp; Authorization Service</t>
+  </si>
+  <si>
+    <t>Exam Management + Evaluation Engine</t>
+  </si>
+  <si>
+    <t>Submission only by owner before end+5s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,13 +541,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F497D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E3F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -490,64 +614,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -556,40 +622,113 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -906,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E9E6B2-97C5-4A82-94EE-5CF8E921866D}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -916,606 +1055,716 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A57" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="3" t="s">
+    <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+    <row r="62" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A47" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>5</v>
+      <c r="D64" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A57:D57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
